--- a/product_upload/packages/28/file.xlsx
+++ b/product_upload/packages/28/file.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -596,7 +596,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -645,6 +645,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -669,7 +674,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -844,6 +849,11 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>QUETTA XR 200 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-AAA48FA63524</t>
         </is>
       </c>
@@ -867,7 +877,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1042,6 +1052,11 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>MODEXA 30 mg gastro-resistant capsule</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-0BF77BC95F21</t>
         </is>
       </c>
@@ -1065,7 +1080,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1232,6 +1247,11 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>MINOCET 300 mg capsule</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-2DDFA32ACA1C</t>
         </is>
       </c>
@@ -1255,7 +1275,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1418,6 +1438,11 @@
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>MINOCET 125 mg/5 ml powder for oral suspension</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-D0518C2C5033</t>
         </is>
       </c>
@@ -1441,7 +1466,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1604,6 +1629,11 @@
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>MINOCET 125 mg/5 ml powder for oral suspension</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-BF9F0475DB61</t>
         </is>
       </c>
@@ -1627,7 +1657,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1802,6 +1832,11 @@
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>RYZODEG FlexTouch 100 u/ml</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-B7F98173035E</t>
         </is>
       </c>
@@ -1825,7 +1860,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1996,6 +2031,11 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>ALEVE 220 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-5ADA4A8B3001</t>
         </is>
       </c>
@@ -2019,7 +2059,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2178,6 +2218,11 @@
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>OCUFLOXIN 3 mg/ml ophthamic solution</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-C36B381F5949</t>
         </is>
       </c>
@@ -2201,7 +2246,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2368,6 +2413,11 @@
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>DICLOPID 50 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-3B8A97FE00CB</t>
         </is>
       </c>
@@ -2391,7 +2441,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2570,6 +2620,11 @@
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>ASPIRIN PROTECT 100MG E.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-509824B0B19F</t>
         </is>
       </c>
@@ -2593,7 +2648,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2764,6 +2819,11 @@
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>MODEXA 60 mg gastro-resistant capsule</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-90DF20C51928</t>
         </is>
       </c>
@@ -2787,7 +2847,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2962,6 +3022,11 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>CIPROGRAM 750 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-58B59C9971FA</t>
         </is>
       </c>
@@ -2985,7 +3050,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3156,6 +3221,11 @@
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>VFONAZ 200 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-A5A4B3D28229</t>
         </is>
       </c>
@@ -3179,7 +3249,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3346,6 +3416,11 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>REZAL XR 50 mg extended-release tablet</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-EE9BAE7E7CB9</t>
         </is>
       </c>
@@ -3369,7 +3444,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3536,6 +3611,11 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>REZAL XR 200 mg extended-release tablet</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-133C7FA0882D</t>
         </is>
       </c>
@@ -3559,7 +3639,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3726,6 +3806,11 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>REZAL XR 300 mg extended-release tablet</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-CCDA9D8E553C</t>
         </is>
       </c>
@@ -3749,7 +3834,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3924,6 +4009,11 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>PHLEBODIA 600 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-CC3CB536FBFA</t>
         </is>
       </c>
@@ -3947,7 +4037,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4122,6 +4212,11 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>VEGA 50 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-BB714567F0EC</t>
         </is>
       </c>
@@ -4145,7 +4240,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4316,6 +4411,11 @@
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>KLARE 500 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-78E5CAEBCB86</t>
         </is>
       </c>
@@ -4339,7 +4439,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4510,6 +4610,11 @@
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>CANDAN 16 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-F865F5BB1E40</t>
         </is>
       </c>
@@ -4533,7 +4638,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4704,6 +4809,11 @@
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>CANDAN PLUS 16/12.5 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-142B247E58AA</t>
         </is>
       </c>
@@ -4727,7 +4837,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4898,6 +5008,11 @@
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>SNAFI 20MG TAB</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-6DC04CD91B25</t>
         </is>
       </c>
@@ -4921,7 +5036,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -5096,6 +5211,11 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>SAVIR 5% cream</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-DCE149EAEE4C</t>
         </is>
       </c>
@@ -5119,7 +5239,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5294,6 +5414,11 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>PROTENSE 40 mg/5 ml oral solution</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-CBB97FCCA3C3</t>
         </is>
       </c>
@@ -5317,7 +5442,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5492,6 +5617,11 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>EZECHOL 10 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-2009371EE9B1</t>
         </is>
       </c>
@@ -5515,7 +5645,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5686,6 +5816,11 @@
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>SETAPRO 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-4CCE1378E333</t>
         </is>
       </c>
@@ -5709,7 +5844,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5884,6 +6019,11 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>SETAPRO 10 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-26A57638B744</t>
         </is>
       </c>
@@ -5907,7 +6047,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -6082,6 +6222,11 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>CIPROGRAM 500 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-C4976FAEC03C</t>
         </is>
       </c>
@@ -6105,7 +6250,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6268,6 +6413,11 @@
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>G-PRIDE 4 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-B1B71121173D</t>
         </is>
       </c>
@@ -6291,7 +6441,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6454,6 +6604,11 @@
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>VERO 100 mg film-coated tablets</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-AB5390B1CFD8</t>
         </is>
       </c>
@@ -6477,7 +6632,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Puerto Rico</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6648,6 +6803,11 @@
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>INVOKANA 100 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-F12F57D413C2</t>
         </is>
       </c>
@@ -6671,7 +6831,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6842,6 +7002,11 @@
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>EPITAM 250 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-9AC32A7907E9</t>
         </is>
       </c>
@@ -6865,7 +7030,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -7036,6 +7201,11 @@
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>EPITAM 500 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-35959BF872C3</t>
         </is>
       </c>
@@ -7059,7 +7229,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -7230,6 +7400,11 @@
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>EPITAM 100 mg/ml syrup</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-F3FF32EE4C07</t>
         </is>
       </c>
@@ -7253,7 +7428,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7424,6 +7599,11 @@
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>MEGAMOX ES 600 mg powder for oral suspension</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-4AFBF425B64E</t>
         </is>
       </c>
@@ -7447,7 +7627,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7614,6 +7794,11 @@
       </c>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>PROLAX ER 15 mg extended-release capsule</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-26BB06DE79D6</t>
         </is>
       </c>
@@ -7637,7 +7822,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7804,6 +7989,11 @@
       </c>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>PROLAX ER 30 mg extended-release capsule</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-FD43D8A04306</t>
         </is>
       </c>
@@ -7827,7 +8017,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7990,6 +8180,11 @@
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>AMLOR PLUS 5/320 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-9BDE159A87C4</t>
         </is>
       </c>
@@ -8013,7 +8208,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -8184,6 +8379,11 @@
       </c>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>Avysk Plus 5/160 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-77786DD718C2</t>
         </is>
       </c>
@@ -8207,7 +8407,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8370,6 +8570,11 @@
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>AMLOR PLUS 10/320 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-F0724DA4736C</t>
         </is>
       </c>
@@ -8393,7 +8598,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8560,6 +8765,11 @@
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>Avysk Plus 10/160 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-B0119FC7B700</t>
         </is>
       </c>
@@ -8583,7 +8793,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8746,6 +8956,11 @@
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>LEVACIN 500 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-CCF6EB54B061</t>
         </is>
       </c>
@@ -8769,7 +8984,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8932,6 +9147,11 @@
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>ARPENIA 15 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-3EF4EFF9ECA1</t>
         </is>
       </c>
@@ -8955,7 +9175,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -9118,6 +9338,11 @@
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>ARPENIA 10 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-633DAEF5EE49</t>
         </is>
       </c>
@@ -9141,7 +9366,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -9316,6 +9541,11 @@
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>CRESCHOL 5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-86906578BF3B</t>
         </is>
       </c>
@@ -9339,7 +9569,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9518,6 +9748,11 @@
       </c>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>CRESCHOL 10 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-614C4C58820B</t>
         </is>
       </c>
@@ -9541,7 +9776,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9720,6 +9955,11 @@
       </c>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>CRESCHOL 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-A147E3DC90B1</t>
         </is>
       </c>
@@ -9743,7 +9983,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9914,6 +10154,11 @@
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>ZEMENTA 10 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-A55F3538FD30</t>
         </is>
       </c>
@@ -9937,7 +10182,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -10100,6 +10345,11 @@
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>ZEMENTA 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-95EFA8D11E30</t>
         </is>
       </c>
@@ -10123,7 +10373,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10298,6 +10548,11 @@
       </c>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>GLANDY 30 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-08409CA9284A</t>
         </is>
       </c>
@@ -10321,7 +10576,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10492,6 +10747,11 @@
       </c>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>CALMTROL 1 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-EF8F42CF1B2D</t>
         </is>
       </c>
@@ -10515,7 +10775,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10682,6 +10942,11 @@
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>CALMTROL 2 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-75DBF96B8897</t>
         </is>
       </c>
@@ -10705,7 +10970,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10872,6 +11137,11 @@
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>CALMTROL 4 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-AA897474FCF3</t>
         </is>
       </c>
@@ -10895,7 +11165,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -11062,6 +11332,11 @@
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>ALOPEXY 5% topical solution</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-DD65C1FEC9DC</t>
         </is>
       </c>
@@ -11085,7 +11360,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -11256,6 +11531,11 @@
       </c>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>ALOPEXY 5% topical solution</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-4CC1039EBB4E</t>
         </is>
       </c>
@@ -11279,7 +11559,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11450,6 +11730,11 @@
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>HEROX 5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-1431BEA7C54A</t>
         </is>
       </c>
@@ -11473,7 +11758,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11640,6 +11925,11 @@
       </c>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>HEROX 5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-AB6A7BEC81A0</t>
         </is>
       </c>
@@ -11663,7 +11953,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11838,6 +12128,11 @@
       </c>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>HEROX 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-33784D45E724</t>
         </is>
       </c>
@@ -11861,7 +12156,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -12028,6 +12323,11 @@
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>HEROX 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-F4007F93EB6B</t>
         </is>
       </c>
@@ -12051,7 +12351,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -12218,6 +12518,11 @@
       </c>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>VEGA 100 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-4311BF83074E</t>
         </is>
       </c>
@@ -12241,7 +12546,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12412,6 +12717,11 @@
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>ENDOMETRIN 100 mg vafinal tablet</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-36239D5327B7</t>
         </is>
       </c>
@@ -12435,7 +12745,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12606,6 +12916,11 @@
       </c>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>LOCASONE M cream</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-98D867F96FEC</t>
         </is>
       </c>
@@ -12629,7 +12944,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12804,6 +13119,11 @@
       </c>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>LERCADIP 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-02A9CE13EBE1</t>
         </is>
       </c>
@@ -12827,7 +13147,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12998,6 +13318,11 @@
       </c>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>LOCASONE M cream</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-7F9CAEE4CC2E</t>
         </is>
       </c>
@@ -13021,7 +13346,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -13188,6 +13513,11 @@
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>LOCASONE M cream</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-C5B2FFDE080C</t>
         </is>
       </c>
@@ -13211,7 +13541,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -13382,6 +13712,11 @@
       </c>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>ADACEL 0.5 ml suspension for injection</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-5AFD06C443C9</t>
         </is>
       </c>
@@ -13405,7 +13740,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13576,6 +13911,11 @@
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>FORXIGA 10 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-9E41AD497E40</t>
         </is>
       </c>
@@ -13599,7 +13939,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13770,6 +14110,11 @@
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>FORXIGA 5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-ECC1CB9BCA76</t>
         </is>
       </c>
@@ -13793,7 +14138,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13972,6 +14317,11 @@
       </c>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>BUTRANS 5 mcg/hour transdermal patch</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-33E4AB2494F3</t>
         </is>
       </c>
@@ -13995,7 +14345,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -14166,6 +14516,11 @@
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>BUTRANS 10 mcg/hour transdermal patch</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-2EB986912FED</t>
         </is>
       </c>
@@ -14189,7 +14544,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -14364,6 +14719,11 @@
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>BUTRANS 20 mcg/hour transdermal patch</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-893E311DD880</t>
         </is>
       </c>
@@ -14387,7 +14747,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -14558,6 +14918,11 @@
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>EPITAM 750 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-F3121DB23C42</t>
         </is>
       </c>
@@ -14581,7 +14946,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14744,6 +15109,11 @@
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>G-PRIDE 3 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-B6E79860ECFA</t>
         </is>
       </c>
@@ -14767,7 +15137,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14934,6 +15304,11 @@
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>LOCASONE M cream</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-92562D2A3873</t>
         </is>
       </c>
@@ -14957,7 +15332,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -15128,6 +15503,11 @@
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>CIPROGRAM 250 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-9E64883BF78B</t>
         </is>
       </c>
@@ -15151,7 +15531,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -15326,6 +15706,11 @@
       </c>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>IROVEL PLUS 150/12.5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-1AEA5AEE766C</t>
         </is>
       </c>
@@ -15349,7 +15734,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -15524,6 +15909,11 @@
       </c>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>IROVEL PLUS 300/12.5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-9298B097CA43</t>
         </is>
       </c>
@@ -15547,7 +15937,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15718,6 +16108,11 @@
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>IROVEL PLUS 300/25 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-11B93ABCB8A1</t>
         </is>
       </c>
@@ -15741,7 +16136,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15904,6 +16299,11 @@
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>LEVETAM 1000 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-23E3DE4E32F2</t>
         </is>
       </c>
@@ -15927,7 +16327,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -16102,6 +16502,11 @@
       </c>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>CREVAST 5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-48678A66B6AF</t>
         </is>
       </c>
@@ -16125,7 +16530,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -16296,6 +16701,11 @@
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>CREVAST 10 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-B2EC45784546</t>
         </is>
       </c>
@@ -16319,7 +16729,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -16494,6 +16904,11 @@
       </c>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>CREVAST 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-CF5650AD487C</t>
         </is>
       </c>
@@ -16517,7 +16932,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16688,6 +17103,11 @@
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>CREVAST 40 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-A09E9CB9CF43</t>
         </is>
       </c>
@@ -16711,7 +17131,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16890,6 +17310,11 @@
       </c>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>TECFIDERA 240 mg capsule</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-2C0391614858</t>
         </is>
       </c>
@@ -16913,7 +17338,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -17092,6 +17517,11 @@
       </c>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>TECFIDERA 120 mg capsule</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-82D5AF5DB180</t>
         </is>
       </c>
@@ -17115,7 +17545,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -17290,6 +17720,11 @@
       </c>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>OXYCONTIN 15 mg controlled release tablet</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-403E3E7EB137</t>
         </is>
       </c>
@@ -17313,7 +17748,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -17480,6 +17915,11 @@
       </c>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>OXYCONTIN 20 mg controlled release tablet</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-0BACCBFA1861</t>
         </is>
       </c>
@@ -17503,7 +17943,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -17678,6 +18118,11 @@
       </c>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>OXYCONTIN 30 mg controlled release tablet</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-C61AAD13843C</t>
         </is>
       </c>
@@ -17701,7 +18146,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17868,6 +18313,11 @@
       </c>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>OXYCONTIN 40 mg controlled release tablet</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-E42D57383B17</t>
         </is>
       </c>
@@ -17891,7 +18341,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -18054,6 +18504,11 @@
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>OXYCONTIN 60 mg controlled release tablet</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-E1F72AEF530C</t>
         </is>
       </c>
@@ -18077,7 +18532,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -18256,6 +18711,11 @@
       </c>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>CONTRA 15/200 mg softgel capsule</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-2635C68E0A36</t>
         </is>
       </c>
@@ -18279,7 +18739,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -18454,6 +18914,11 @@
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>CANESTEN SOLUTION 1%</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-DE92A30BC4DF</t>
         </is>
       </c>
@@ -18477,7 +18942,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -18648,6 +19113,11 @@
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>CANESTEN CREAM 1%</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-529DBFF0D177</t>
         </is>
       </c>
@@ -18671,7 +19141,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18846,6 +19316,11 @@
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>CANESTEN-1 VAG. CREAM 10%</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-21E5DA273727</t>
         </is>
       </c>
@@ -18869,7 +19344,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -19044,6 +19519,11 @@
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>ASPIRIN EFFERVESCENT WITH VITAMIN C</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-FFB83A20446A</t>
         </is>
       </c>
@@ -19067,7 +19547,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -19234,6 +19714,11 @@
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>TYKERB 250MG F.C. TABLETS</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-E1E6CE289233</t>
         </is>
       </c>
@@ -19257,7 +19742,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -19416,6 +19901,11 @@
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>REVOLADE 25MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-504EC42B6BE1</t>
         </is>
       </c>
@@ -19439,7 +19929,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -19602,6 +20092,11 @@
       </c>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>REVOLADE 50MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-95FB2F553DFC</t>
         </is>
       </c>
@@ -19625,7 +20120,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -19804,6 +20299,11 @@
       </c>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>ZOFRAN 8 mg tablet</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-AAE866A8D51B</t>
         </is>
       </c>
@@ -19827,7 +20327,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19993,6 +20493,11 @@
         </is>
       </c>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>POTASSIUM CHLORIDE in  DEXTROSE and  SODIUM CHLORIDE Injection USP</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-004E53EB70EB</t>
         </is>
@@ -20009,7 +20514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20055,100 +20560,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -20180,7 +20690,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -20195,92 +20705,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-80311</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>17.26</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>208</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20312,7 +20827,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -20327,92 +20842,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-46278</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>32.22</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>209</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20444,7 +20964,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -20459,92 +20979,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-41787</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>143.5</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>210</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20576,7 +21101,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -20591,92 +21116,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-34182</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>487.9</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>211</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20708,7 +21238,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20723,92 +21253,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-26470</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>131.36</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>212</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20840,7 +21375,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20855,92 +21390,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-21891</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>358.06</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>213</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20972,7 +21512,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20987,92 +21527,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-21129</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>418.5</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>214</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21104,7 +21649,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -21119,92 +21664,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-64431</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>23.5</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>215</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21236,7 +21786,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -21251,92 +21801,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-71484</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>33.83</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>216</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21368,7 +21923,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -21383,92 +21938,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-12439</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>21.49</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>217</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21500,7 +22060,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -21515,92 +22075,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-96777</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>265.7</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>218</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21617,7 +22182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21723,6 +22288,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -21758,7 +22333,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21823,6 +22398,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-AB836AEBDC3D</t>
         </is>
@@ -21859,7 +22444,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21924,6 +22509,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-EB224DB8D8F9</t>
         </is>
@@ -21960,7 +22555,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -22025,6 +22620,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-8F09CC9BACCE</t>
         </is>
@@ -22061,7 +22666,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -22126,6 +22731,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-4292A6B53E1A</t>
         </is>
@@ -22162,7 +22777,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -22227,6 +22842,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-666E9F625762</t>
         </is>
@@ -22263,7 +22888,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -22328,6 +22953,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-ECD3406E1202</t>
         </is>
@@ -22364,7 +22999,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -22429,6 +23064,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-1B73455EC02C</t>
         </is>
@@ -22465,7 +23110,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -22530,6 +23175,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-1422F67F2BA7</t>
         </is>
@@ -22566,7 +23221,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -22631,6 +23286,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-49FB80C5A989</t>
         </is>
@@ -22667,7 +23332,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -22732,6 +23397,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-B3B955660D19</t>
         </is>
@@ -22768,7 +23443,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22833,6 +23508,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-343065FE3764</t>
         </is>
@@ -22869,7 +23554,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22934,6 +23619,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-9EAD16040865</t>
         </is>
@@ -22970,7 +23665,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -23035,6 +23730,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-9AF441695FD7</t>
         </is>
@@ -23071,7 +23776,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -23136,6 +23841,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-1F0B8F4177D0</t>
         </is>
@@ -23172,7 +23887,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -23237,6 +23952,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-D7D415F9CD80</t>
         </is>
@@ -23273,7 +23998,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -23338,6 +24063,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-DA8E70066399</t>
         </is>
@@ -23374,7 +24109,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -23439,6 +24174,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-F729EF482566</t>
         </is>
@@ -23475,7 +24220,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -23540,6 +24285,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-9777C2648A57</t>
         </is>
@@ -23576,7 +24331,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -23641,6 +24396,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-1F968F84BFFC</t>
         </is>
@@ -23677,7 +24442,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -23742,6 +24507,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-BAE90AF27875</t>
         </is>

--- a/product_upload/packages/28/file.xlsx
+++ b/product_upload/packages/28/file.xlsx
@@ -1088,8 +1088,16 @@
           <t>3140210178-074-710173143314</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MINOCET 300 mg capsule</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>MINOCET 300 mg capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1283,8 +1291,16 @@
           <t>7544969542-464-068794589994</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MINOCET 125 mg/5 ml powder for oral suspension</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>MINOCET 125 mg/5 ml powder for oral suspension detailed description.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>0</t>
@@ -1474,8 +1490,16 @@
           <t>7656181493-990-221169362629</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MINOCET 125 mg/5 ml powder for oral suspension</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>MINOCET 125 mg/5 ml powder for oral suspension detailed description.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>0</t>
@@ -1868,8 +1892,16 @@
           <t>3443859034-013-410087066981</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ALEVE 220 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>ALEVE 220 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>0</t>
@@ -2067,8 +2099,16 @@
           <t>6407435151-524-295252292477</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OCUFLOXIN 3 mg/ml ophthamic solution</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>OCUFLOXIN 3 mg/ml ophthamic solution detailed description.</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>0</t>
@@ -2254,8 +2294,16 @@
           <t>0684175466-634-711523462299</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DICLOPID 50 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>DICLOPID 50 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>0</t>
@@ -3257,8 +3305,16 @@
           <t>2180857775-807-473136191720</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ REZAL XR 50 mg extended-release tablet</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>REZAL XR 50 mg extended-release tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>0</t>
@@ -3452,8 +3508,16 @@
           <t>5826845397-183-836517440177</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ REZAL XR 200 mg extended-release tablet</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>REZAL XR 200 mg extended-release tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>0</t>
@@ -3647,8 +3711,16 @@
           <t>9056323635-288-060852983354</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ REZAL XR 300 mg extended-release tablet</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>REZAL XR 300 mg extended-release tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>0</t>
@@ -6258,8 +6330,16 @@
           <t>9824245013-448-007372578415</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ G-PRIDE 4 mg tablet</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>G-PRIDE 4 mg tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>0</t>
@@ -6449,8 +6529,16 @@
           <t>7393617250-160-496263212237</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VERO 100 mg film-coated tablets</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>VERO 100 mg film-coated tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>0</t>
@@ -7635,8 +7723,16 @@
           <t>6298788570-924-269029040254</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PROLAX ER 15 mg extended-release capsule</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>PROLAX ER 15 mg extended-release capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>0</t>
@@ -7830,8 +7926,16 @@
           <t>6978802429-819-964821896428</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ PROLAX ER 30 mg extended-release capsule</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>PROLAX ER 30 mg extended-release capsule detailed description.</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr">
         <is>
           <t>0</t>
@@ -8025,8 +8129,16 @@
           <t>3054371459-498-970985239723</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AMLOR PLUS 5/320 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>AMLOR PLUS 5/320 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr">
         <is>
           <t>0</t>
@@ -8216,8 +8328,16 @@
           <t>6150707214-953-810202760446</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Avysk Plus 5/160 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Avysk Plus 5/160 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>0</t>
@@ -8415,8 +8535,16 @@
           <t>3835731650-311-679224221996</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AMLOR PLUS 10/320 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>AMLOR PLUS 10/320 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>0</t>
@@ -8606,8 +8734,16 @@
           <t>1222183558-304-674479829694</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Avysk Plus 10/160 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Avysk Plus 10/160 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr">
         <is>
           <t>0</t>
@@ -8801,8 +8937,16 @@
           <t>1451610849-327-621312326469</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LEVACIN 500 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>LEVACIN 500 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr">
         <is>
           <t>0</t>
@@ -8992,8 +9136,16 @@
           <t>2636713832-046-071664288378</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ARPENIA 15 mg tablet</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>ARPENIA 15 mg tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr">
         <is>
           <t>0</t>
@@ -9183,8 +9335,16 @@
           <t>6533855245-041-978704726520</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ARPENIA 10 mg tablet</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>ARPENIA 10 mg tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr">
         <is>
           <t>0</t>
@@ -10190,8 +10350,16 @@
           <t>0590820021-287-623866688574</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZEMENTA 20 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>ZEMENTA 20 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I50" t="inlineStr">
         <is>
           <t>0</t>
@@ -10584,8 +10752,16 @@
           <t>5872679041-140-642198712226</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CALMTROL 1 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>CALMTROL 1 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr">
         <is>
           <t>0</t>
@@ -10783,8 +10959,16 @@
           <t>7601525357-190-856076117893</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CALMTROL 2 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>CALMTROL 2 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr">
         <is>
           <t>0</t>
@@ -10978,8 +11162,16 @@
           <t>7652007041-508-001179976488</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CALMTROL 4 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>CALMTROL 4 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr">
         <is>
           <t>0</t>
@@ -11173,8 +11365,16 @@
           <t>4286052515-431-718200414072</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ALOPEXY 5% topical solution</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>ALOPEXY 5% topical solution detailed description.</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr">
         <is>
           <t>0</t>
@@ -11368,8 +11568,16 @@
           <t>6765176014-043-703423228170</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ALOPEXY 5% topical solution</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>ALOPEXY 5% topical solution detailed description.</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr">
         <is>
           <t>0</t>
@@ -11766,8 +11974,16 @@
           <t>4220370871-785-711279096710</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ HEROX 5 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>HEROX 5 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr">
         <is>
           <t>0</t>
@@ -12359,8 +12575,16 @@
           <t>8161344184-822-669809612765</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VEGA 100 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>VEGA 100 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr">
         <is>
           <t>0</t>
@@ -12753,8 +12977,16 @@
           <t>4274783192-554-342921643698</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LOCASONE M cream</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>LOCASONE M cream detailed description.</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr">
         <is>
           <t>0</t>
@@ -13155,8 +13387,16 @@
           <t>3491603423-546-520684983781</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LOCASONE M cream</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>LOCASONE M cream detailed description.</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr">
         <is>
           <t>0</t>
@@ -13354,8 +13594,16 @@
           <t>6266662224-705-892589926188</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LOCASONE M cream</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>LOCASONE M cream detailed description.</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr">
         <is>
           <t>0</t>
@@ -13549,8 +13797,16 @@
           <t>7479365294-410-307696828471</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ADACEL 0.5 ml suspension for injection</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>ADACEL 0.5 ml suspension for injection detailed description.</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr">
         <is>
           <t>0</t>
@@ -14954,8 +15210,16 @@
           <t>2613850155-575-374227575608</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ G-PRIDE 3 mg tablet</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>G-PRIDE 3 mg tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr">
         <is>
           <t>0</t>
@@ -15145,8 +15409,16 @@
           <t>2618044457-714-482585516484</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LOCASONE M cream</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>LOCASONE M cream detailed description.</t>
+        </is>
+      </c>
       <c r="I75" t="inlineStr">
         <is>
           <t>0</t>
@@ -16144,8 +16416,16 @@
           <t>7167461515-657-829738543302</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LEVETAM 1000 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>LEVETAM 1000 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr">
         <is>
           <t>SPIMACO</t>
@@ -17756,8 +18036,16 @@
           <t>9964987916-547-678234987642</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OXYCONTIN 20 mg controlled release tablet</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>OXYCONTIN 20 mg controlled release tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr">
         <is>
           <t>0</t>
@@ -18154,8 +18442,16 @@
           <t>7582547325-896-401206760313</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OXYCONTIN 40 mg controlled release tablet</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>OXYCONTIN 40 mg controlled release tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr">
         <is>
           <t>0</t>
@@ -18349,8 +18645,16 @@
           <t>9294552571-473-243505582282</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OXYCONTIN 60 mg controlled release tablet</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>OXYCONTIN 60 mg controlled release tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I91" t="inlineStr">
         <is>
           <t>0</t>
@@ -19750,8 +20054,16 @@
           <t>5863814253-506-805361911513</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ REVOLADE 25MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>REVOLADE 25MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr">
         <is>
           <t>0</t>
@@ -19937,8 +20249,16 @@
           <t>2778035524-013-662241072809</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ REVOLADE 50MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>REVOLADE 50MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I99" t="inlineStr">
         <is>
           <t>0</t>
@@ -20335,8 +20655,16 @@
           <t>7733077994-860-506135206965</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ POTASSIUM CHLORIDE in  DEXTROSE and  SODIUM CHLORIDE Injection USP</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>POTASSIUM CHLORIDE in  DEXTROSE and  SODIUM CHLORIDE Injection USP detailed description.</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr">
         <is>
           <t>0</t>

--- a/product_upload/packages/28/file.xlsx
+++ b/product_upload/packages/28/file.xlsx
@@ -596,7 +596,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20888,7 +20888,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -22510,7 +22510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22591,40 +22591,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22704,38 +22709,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>438.03</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-AB836AEBDC3D</t>
         </is>
@@ -22815,38 +22825,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>188.99</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-EB224DB8D8F9</t>
         </is>
@@ -22926,38 +22941,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>243.51</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-8F09CC9BACCE</t>
         </is>
@@ -23037,38 +23057,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>124.97</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-4292A6B53E1A</t>
         </is>
@@ -23148,38 +23173,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>358.59</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-666E9F625762</t>
         </is>
@@ -23259,38 +23289,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>253.75</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-ECD3406E1202</t>
         </is>
@@ -23370,38 +23405,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>430.06</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-1B73455EC02C</t>
         </is>
@@ -23481,38 +23521,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>204.12</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-1422F67F2BA7</t>
         </is>
@@ -23592,38 +23637,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>237.33</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-49FB80C5A989</t>
         </is>
@@ -23703,38 +23753,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>277.52</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-B3B955660D19</t>
         </is>
@@ -23814,38 +23869,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>357.54</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-343065FE3764</t>
         </is>
@@ -23925,38 +23985,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>434.89</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-9EAD16040865</t>
         </is>
@@ -24036,38 +24101,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>254.99</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-9AF441695FD7</t>
         </is>
@@ -24147,38 +24217,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>432.75</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-1F0B8F4177D0</t>
         </is>
@@ -24258,38 +24333,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>276.66</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-D7D415F9CD80</t>
         </is>
@@ -24369,38 +24449,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>363.9</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-DA8E70066399</t>
         </is>
@@ -24480,38 +24565,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>479.84</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-F729EF482566</t>
         </is>
@@ -24591,38 +24681,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>55.59</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-9777C2648A57</t>
         </is>
@@ -24702,38 +24797,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>206.56</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-1F968F84BFFC</t>
         </is>
@@ -24813,38 +24913,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>11.37</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-BAE90AF27875</t>
         </is>
